--- a/songs/Firework_v1/quelle/struktur.xlsx
+++ b/songs/Firework_v1/quelle/struktur.xlsx
@@ -436,15 +436,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,6 +469,7 @@
       <c r="C2" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -478,6 +480,7 @@
       <c r="C3" s="2" t="n">
         <v>124</v>
       </c>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -488,6 +491,7 @@
       <c r="C4" s="2" t="n">
         <v>0.25</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -502,20 +506,25 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Effektidee</t>
+          <t>Effekt (füllt KI)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>Änderungswunsch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -530,13 +539,19 @@
           <t>text</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlack(6290, 2)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6290, 2)</t>
         </is>
@@ -551,13 +566,19 @@
           <t>snarewirbel</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(970, 5, 50, getRandomCRGB())   (Matrix: progScrollText("Firework by Katy Perry", 16500, 90, getRandomColor(), 10))</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(970, 5, 50, getRandomCRGB())   (Matrix: progScrollText("Firework by Katy Perry", 16500, 90, getRandomColor(), 10))</t>
         </is>
@@ -572,13 +593,19 @@
           <t>intro1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(15480, 970, 10, 5, 26, 5, false, 4)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15480, 970, 10, 5, 26, 5, false, 4)</t>
         </is>
@@ -593,13 +620,19 @@
           <t>verse 1a</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progBlingBlingColoring(30970, 20, 3000)</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(30970, 20, 3000)</t>
         </is>
@@ -614,13 +647,19 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13550, 4, 22)</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13550, 4, 22)</t>
         </is>
@@ -635,13 +674,19 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 24, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 24, 50, getRandomCRGB())</t>
         </is>
@@ -656,13 +701,20 @@
           <t>chorus 1</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(14500, 970, 26, 5, 26, 5, true, 3)
+! Excel: 7 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14500, 970, 26, 5, 26, 5, true, 3)
 ! Excel: 7 Takte, der alte Code ist anders</t>
@@ -678,13 +730,20 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1000, 30, 50, getRandomCRGB())
+! Excel: 1 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 30, 50, getRandomCRGB())
 ! Excel: 1 Takte, der alte Code ist anders</t>
@@ -700,13 +759,19 @@
           <t>verse 2a</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFullColors(15475, 32, 485)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15475, 32, 485)</t>
         </is>
@@ -721,13 +786,19 @@
           <t>verse 2b</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progCircles(15475, 34, 485)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>progCircles(15475, 34, 485)</t>
         </is>
@@ -742,13 +813,20 @@
           <t>bridge</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(13550, 5, 35)
+! Excel: 8 Takte, der alte Code ist anders</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>progPalette(13550, 5, 35)
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -764,13 +842,19 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1925, 36, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1925, 36, 50, getRandomCRGB())</t>
         </is>
@@ -785,13 +869,19 @@
           <t>chorus 2a</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(14500, 37, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14500, 37, 50, true, false)</t>
         </is>
@@ -806,13 +896,19 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1000, 40, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 40, 50, getRandomCRGB())</t>
         </is>
@@ -827,13 +923,19 @@
           <t>BOOM 1</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15485, 2, 42)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>progPalette(15485, 2, 42)</t>
         </is>
@@ -848,13 +950,19 @@
           <t>nur vocals</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+matrixMovieFX(15485, 44, 100, 6)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(15485, 44, 100, 6)</t>
         </is>
@@ -869,13 +977,19 @@
           <t>BOOM 3</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progPalette(15485, 7, 46)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>progPalette(15485, 7, 46)</t>
         </is>
@@ -890,13 +1004,19 @@
           <t>BOOM 4</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progWaterRipple(13550, 47, 50, true, false)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(13550, 47, 50, true, false)</t>
         </is>
@@ -911,13 +1031,19 @@
           <t>strobo snarewirbel</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1935, 50, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 50, 50, getRandomCRGB())</t>
         </is>
@@ -932,13 +1058,19 @@
           <t>chorus 2a</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progSternNeu(14500, 970, 52, 15, 26, 5, true, 3)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14500, 970, 52, 15, 26, 5, true, 3)</t>
         </is>
@@ -953,13 +1085,19 @@
           <t>übergang</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(1000, 54, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 54, 50, getRandomCRGB())</t>
         </is>
@@ -974,13 +1112,19 @@
           <t>chorus 2</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progFastBlingBling(14515, 10, 56)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14515, 10, 56)</t>
         </is>
@@ -995,13 +1139,19 @@
           <t>strobo snarewirbel</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>alter Code (handgeschrieben, läuft so in der Firmware):
+progStrobo(970, 60, 50, getRandomCRGB())</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(970, 60, 50, getRandomCRGB())</t>
         </is>
@@ -1021,10 +1171,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <f>$C$3</f>
         <v/>
       </c>

--- a/songs/Firework_v1/quelle/struktur.xlsx
+++ b/songs/Firework_v1/quelle/struktur.xlsx
@@ -532,7 +532,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -640,7 +640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -667,7 +667,7 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>123.5</v>
+        <v>124.5</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="29">
       <c r="A29" s="7" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>

--- a/songs/Firework_v1/quelle/struktur.xlsx
+++ b/songs/Firework_v1/quelle/struktur.xlsx
@@ -436,16 +436,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,6 +471,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="B3" t="inlineStr">
@@ -481,6 +483,7 @@
         <v>124</v>
       </c>
       <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
@@ -492,6 +495,7 @@
         <v>0.25</v>
       </c>
       <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -516,15 +520,20 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
+          <t>Neuer Vorschlag (KI)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>Energie 0-5</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>BPM pro Part</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>bisher (alter Code)</t>
         </is>
@@ -546,12 +555,13 @@
         </is>
       </c>
       <c r="D6" s="6" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>progBlack(6290, 2)</t>
         </is>
@@ -573,12 +583,13 @@
         </is>
       </c>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>progStrobo(970, 5, 50, getRandomCRGB())   (Matrix: progScrollText("Firework by Katy Perry", 16500, 90, getRandomColor(), 10))</t>
         </is>
@@ -600,12 +611,17 @@
         </is>
       </c>
       <c r="D8" s="6" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Stern bleibt, in ROYAL mit weichen Farbwechseln (soft 60) - ruhiger Anfang.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(15480, 970, 10, 5, 26, 5, false, 4)</t>
         </is>
@@ -627,12 +643,18 @@
         </is>
       </c>
       <c r="D9" s="6" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>16 Takte ein Effekt sind lang. Szene Glow, ROYAL, Farbwanderung (triad, 2 Takte).
+Besser: bei Takt 21 eine eigene Zeile "verse 1b" anlegen - dann ab dort Szene Rain als kleine Steigerung.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>progBlingBlingColoring(30970, 20, 3000)</t>
         </is>
@@ -654,12 +676,17 @@
         </is>
       </c>
       <c r="D10" s="6" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Szene Palette, SUNSET, darüber baut sich ein Glitzern auf (Ebene Sparkle, fade_in über 7 Takte) - "ignite the light".</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
         <is>
           <t>progPalette(13550, 4, 22)</t>
         </is>
@@ -681,12 +708,17 @@
         </is>
       </c>
       <c r="D11" s="6" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Weißer Strobo (statt Zufallsfarbe) als Absprung.</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 24, 50, getRandomCRGB())</t>
         </is>
@@ -709,12 +741,17 @@
         </is>
       </c>
       <c r="D12" s="6" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, SUNSET, Blinder auf den Einsatz (2 Beats). Auf der Matrix "FIREWORK" über dem Stern, blendet nach 2 Takten aus.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14500, 970, 26, 5, 26, 5, true, 3)
 ! Excel: 7 Takte, der alte Code ist anders</t>
@@ -738,12 +775,13 @@
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 30, 50, getRandomCRGB())
 ! Excel: 1 Takte, der alte Code ist anders</t>
@@ -766,12 +804,17 @@
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Szene Colors, NEON, soft 30: eine Farbe pro Beat auf der ganzen Bühne, mit kurzer Blende.</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
         <is>
           <t>progFullColors(15475, 32, 485)</t>
         </is>
@@ -793,12 +836,17 @@
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Szene Call Response, NEON: die Bühnenhälften blitzen abwechselnd - Steigerung zu verse 2a.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>progCircles(15475, 34, 485)</t>
         </is>
@@ -821,12 +869,17 @@
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>wie bridge 1 (Palette SUNSET + Glitzern baut sich auf).</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>progPalette(13550, 5, 35)
 ! Excel: 8 Takte, der alte Code ist anders</t>
@@ -849,12 +902,13 @@
         </is>
       </c>
       <c r="D17" s="6" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1925, 36, 50, getRandomCRGB())</t>
         </is>
@@ -876,12 +930,17 @@
         </is>
       </c>
       <c r="D18" s="6" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Szene Fire, FIRE statt Wasserringe: Feuer auf allen Geräten, Blinder auf den Einsatz. Text "FIREWORK" wie in chorus 1.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(14500, 37, 50, true, false)</t>
         </is>
@@ -903,12 +962,13 @@
         </is>
       </c>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 40, 50, getRandomCRGB())</t>
         </is>
@@ -930,12 +990,17 @@
         </is>
       </c>
       <c r="D20" s="6" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Szene Drop, SUNSET: Schläge auf die Viertel; dazu Blinder auf jede 1 (jeder Takt, 2 Beats) - "boom boom boom".</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
         <is>
           <t>progPalette(15485, 2, 42)</t>
         </is>
@@ -957,12 +1022,17 @@
         </is>
       </c>
       <c r="D21" s="6" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Szene Calm, BLUE, auf 50 % gedimmt, weich eingeblendet (fade, 4 Beats): die Bühne tritt zurück, nur die Stimme.</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>matrixMovieFX(15485, 44, 100, 6)</t>
         </is>
@@ -984,12 +1054,17 @@
         </is>
       </c>
       <c r="D22" s="6" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Szene Wave Out, SUNSET: der Blitz läuft pro Beat von der Mitte nach außen; Blinder auf die 1 (Takt 93).</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
         <is>
           <t>progPalette(15485, 7, 46)</t>
         </is>
@@ -1011,12 +1086,17 @@
         </is>
       </c>
       <c r="D23" s="6" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Wasserringe bleiben, darüber baut sich Glitzern auf (Ebene Sparkle, fade_in 7 Takte) - Anlauf zum Finale.</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
         <is>
           <t>progWaterRipple(13550, 47, 50, true, false)</t>
         </is>
@@ -1038,12 +1118,17 @@
         </is>
       </c>
       <c r="D24" s="6" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Szene Buildup (1 Takt), FIRE: Explosion genau auf den Chorus.</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1935, 50, 50, getRandomCRGB())</t>
         </is>
@@ -1065,12 +1150,17 @@
         </is>
       </c>
       <c r="D25" s="6" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Szene Star, FIRE, Blinder auf den Einsatz; Lampen blitzen weiß auf 2 und 4.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H25" s="6" t="inlineStr">
         <is>
           <t>progSternNeu(14500, 970, 52, 15, 26, 5, true, 3)</t>
         </is>
@@ -1092,12 +1182,13 @@
         </is>
       </c>
       <c r="D26" s="6" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
         <is>
           <t>progStrobo(1000, 54, 50, getRandomCRGB())</t>
         </is>
@@ -1119,12 +1210,17 @@
         </is>
       </c>
       <c r="D27" s="6" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>Szene Sparkle, FIRE - Höhepunkt. Drei kurze Blinder auf den letzten drei Vierteln (Takt 124 / 124,25 / 124,5 = Einsatz des Snarewirbels).</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
         <is>
           <t>progFastBlingBling(14515, 10, 56)</t>
         </is>
@@ -1146,12 +1242,17 @@
         </is>
       </c>
       <c r="D28" s="6" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5">
-        <f>$C$3</f>
-        <v/>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Starker Blinder statt Strobo: voll auf der letzten Viertel (Takt 124,75), klingt 5 Sekunden ins Schluss-Schwarz aus (wie APT.).</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5">
+        <f>$C$3</f>
+        <v/>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
         <is>
           <t>progStrobo(970, 60, 50, getRandomCRGB())</t>
         </is>
@@ -1171,10 +1272,10 @@
           <t>10 sek. BLACK</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0</v>
       </c>
-      <c r="F29">
+      <c r="G29">
         <f>$C$3</f>
         <v/>
       </c>
